--- a/2022 data/excel_outputs/220_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/220_boothwise_data.xlsx
@@ -14,11 +14,89 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="630">
   <si>
     <t>AC 220 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -1603,7 +1681,7 @@
     <t>praathmik vighaaly cndrkuaa koNc</t>
   </si>
   <si>
-    <t>####### ###### ######## ###### ####### #####</t>
+    <t>praathmik vighaaly cndrkuaa koNc ROOM NO. 529</t>
   </si>
   <si>
     <t>shrii naathuuraam purohit baalikaa vighaaly</t>
@@ -1832,8 +1910,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1849,7 +1935,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1857,12 +1943,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2161,91 +2265,169 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>580</v>
+        <v>606</v>
       </c>
       <c r="D2" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="E2" t="s">
-        <v>582</v>
+        <v>608</v>
       </c>
       <c r="F2" t="s">
-        <v>583</v>
+        <v>609</v>
       </c>
       <c r="G2" t="s">
-        <v>584</v>
+        <v>610</v>
       </c>
       <c r="H2" t="s">
-        <v>585</v>
+        <v>611</v>
       </c>
       <c r="I2" t="s">
-        <v>586</v>
+        <v>612</v>
       </c>
       <c r="J2" t="s">
-        <v>587</v>
+        <v>613</v>
       </c>
       <c r="K2" t="s">
-        <v>588</v>
+        <v>614</v>
       </c>
       <c r="L2" t="s">
-        <v>589</v>
+        <v>615</v>
       </c>
       <c r="M2" t="s">
-        <v>590</v>
+        <v>616</v>
       </c>
       <c r="N2" t="s">
-        <v>591</v>
+        <v>617</v>
       </c>
       <c r="O2" t="s">
-        <v>592</v>
+        <v>618</v>
       </c>
       <c r="P2" t="s">
-        <v>593</v>
+        <v>619</v>
       </c>
       <c r="Q2" t="s">
-        <v>594</v>
+        <v>620</v>
       </c>
       <c r="R2" t="s">
-        <v>595</v>
+        <v>621</v>
       </c>
       <c r="S2" t="s">
-        <v>596</v>
+        <v>622</v>
       </c>
       <c r="T2" t="s">
-        <v>597</v>
+        <v>623</v>
       </c>
       <c r="U2" t="s">
-        <v>598</v>
+        <v>624</v>
       </c>
       <c r="V2" t="s">
-        <v>599</v>
+        <v>625</v>
       </c>
       <c r="W2" t="s">
-        <v>600</v>
+        <v>626</v>
       </c>
       <c r="X2" t="s">
-        <v>601</v>
+        <v>627</v>
       </c>
       <c r="Y2" t="s">
-        <v>601</v>
+        <v>627</v>
       </c>
       <c r="Z2" t="s">
-        <v>602</v>
+        <v>628</v>
       </c>
       <c r="AA2" t="s">
-        <v>603</v>
+        <v>629</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -2253,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>858</v>
@@ -2336,7 +2518,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>421</v>
@@ -2419,7 +2601,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>926</v>
@@ -2502,7 +2684,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>1103</v>
@@ -2585,7 +2767,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>324</v>
@@ -2668,7 +2850,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>766</v>
@@ -2751,7 +2933,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>462</v>
@@ -2834,7 +3016,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <v>350</v>
@@ -2917,7 +3099,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>550</v>
@@ -3000,7 +3182,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C12">
         <v>611</v>
@@ -3083,7 +3265,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>290</v>
@@ -3166,7 +3348,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C14">
         <v>770</v>
@@ -3249,7 +3431,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C15">
         <v>907</v>
@@ -3332,7 +3514,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C16">
         <v>1032</v>
@@ -3415,7 +3597,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C17">
         <v>682</v>
@@ -3498,7 +3680,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C18">
         <v>1006</v>
@@ -3581,7 +3763,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C19">
         <v>436</v>
@@ -3664,7 +3846,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C20">
         <v>702</v>
@@ -3747,7 +3929,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C21">
         <v>523</v>
@@ -3830,7 +4012,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C22">
         <v>612</v>
@@ -3913,7 +4095,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C23">
         <v>594</v>
@@ -3996,7 +4178,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C24">
         <v>1113</v>
@@ -4079,7 +4261,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C25">
         <v>419</v>
@@ -4162,7 +4344,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C26">
         <v>248</v>
@@ -4245,7 +4427,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C27">
         <v>813</v>
@@ -4328,7 +4510,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C28">
         <v>1047</v>
@@ -4411,7 +4593,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C29">
         <v>1054</v>
@@ -4494,7 +4676,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C30">
         <v>1073</v>
@@ -4577,7 +4759,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="C31">
         <v>949</v>
@@ -4660,7 +4842,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C32">
         <v>1062</v>
@@ -4743,7 +4925,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C33">
         <v>834</v>
@@ -4826,7 +5008,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C34">
         <v>1035</v>
@@ -4909,7 +5091,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C35">
         <v>1057</v>
@@ -4992,7 +5174,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="C36">
         <v>1118</v>
@@ -5075,7 +5257,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C37">
         <v>897</v>
@@ -5158,7 +5340,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C38">
         <v>825</v>
@@ -5241,7 +5423,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C39">
         <v>804</v>
@@ -5324,7 +5506,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C40">
         <v>1105</v>
@@ -5407,7 +5589,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C41">
         <v>776</v>
@@ -5490,7 +5672,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C42">
         <v>282</v>
@@ -5573,7 +5755,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C43">
         <v>606</v>
@@ -5656,7 +5838,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C44">
         <v>601</v>
@@ -5739,7 +5921,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="C45">
         <v>607</v>
@@ -5822,7 +6004,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C46">
         <v>562</v>
@@ -5905,7 +6087,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="C47">
         <v>349</v>
@@ -5988,7 +6170,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C48">
         <v>531</v>
@@ -6071,7 +6253,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="C49">
         <v>973</v>
@@ -6154,7 +6336,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C50">
         <v>323</v>
@@ -6237,7 +6419,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C51">
         <v>735</v>
@@ -6320,7 +6502,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C52">
         <v>560</v>
@@ -6403,7 +6585,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="C53">
         <v>1126</v>
@@ -6486,7 +6668,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="C54">
         <v>562</v>
@@ -6569,7 +6751,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C55">
         <v>952</v>
@@ -6652,7 +6834,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C56">
         <v>1107</v>
@@ -6735,7 +6917,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C57">
         <v>1153</v>
@@ -6818,7 +7000,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C58">
         <v>600</v>
@@ -6901,7 +7083,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="C59">
         <v>897</v>
@@ -6984,7 +7166,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C60">
         <v>980</v>
@@ -7067,7 +7249,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C61">
         <v>563</v>
@@ -7150,7 +7332,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="C62">
         <v>842</v>
@@ -7233,7 +7415,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C63">
         <v>406</v>
@@ -7316,7 +7498,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="C64">
         <v>795</v>
@@ -7399,7 +7581,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="C65">
         <v>485</v>
@@ -7482,7 +7664,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="C66">
         <v>608</v>
@@ -7565,7 +7747,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="C67">
         <v>588</v>
@@ -7648,7 +7830,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C68">
         <v>1143</v>
@@ -7731,7 +7913,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C69">
         <v>600</v>
@@ -7814,7 +7996,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C70">
         <v>584</v>
@@ -7897,7 +8079,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="C71">
         <v>921</v>
@@ -7980,7 +8162,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C72">
         <v>698</v>
@@ -8063,7 +8245,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="C73">
         <v>741</v>
@@ -8146,7 +8328,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C74">
         <v>499</v>
@@ -8229,7 +8411,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C75">
         <v>516</v>
@@ -8312,7 +8494,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="C76">
         <v>1030</v>
@@ -8395,7 +8577,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="C77">
         <v>446</v>
@@ -8478,7 +8660,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C78">
         <v>890</v>
@@ -8561,7 +8743,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C79">
         <v>331</v>
@@ -8644,7 +8826,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C80">
         <v>1107</v>
@@ -8727,7 +8909,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C81">
         <v>1056</v>
@@ -8810,7 +8992,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="C82">
         <v>1025</v>
@@ -8893,7 +9075,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="C83">
         <v>786</v>
@@ -8976,7 +9158,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="C84">
         <v>583</v>
@@ -9059,7 +9241,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="C85">
         <v>770</v>
@@ -9142,7 +9324,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="C86">
         <v>591</v>
@@ -9225,7 +9407,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="C87">
         <v>724</v>
@@ -9308,7 +9490,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="C88">
         <v>666</v>
@@ -9391,7 +9573,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="C89">
         <v>745</v>
@@ -9474,7 +9656,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="C90">
         <v>615</v>
@@ -9557,7 +9739,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="C91">
         <v>995</v>
@@ -9640,7 +9822,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="C92">
         <v>697</v>
@@ -9723,7 +9905,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="C93">
         <v>854</v>
@@ -9806,7 +9988,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="C94">
         <v>505</v>
@@ -9889,7 +10071,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="C95">
         <v>865</v>
@@ -9972,7 +10154,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="C96">
         <v>856</v>
@@ -10055,7 +10237,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="C97">
         <v>1147</v>
@@ -10138,7 +10320,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="C98">
         <v>790</v>
@@ -10221,7 +10403,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="C99">
         <v>1170</v>
@@ -10304,7 +10486,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="C100">
         <v>862</v>
@@ -10387,7 +10569,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="C101">
         <v>1033</v>
@@ -10470,7 +10652,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C102">
         <v>996</v>
@@ -10553,7 +10735,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="C103">
         <v>371</v>
@@ -10636,7 +10818,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="C104">
         <v>1122</v>
@@ -10719,7 +10901,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="C105">
         <v>977</v>
@@ -10802,7 +10984,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="C106">
         <v>858</v>
@@ -10885,7 +11067,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="C107">
         <v>645</v>
@@ -10968,7 +11150,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="C108">
         <v>634</v>
@@ -11051,7 +11233,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="C109">
         <v>467</v>
@@ -11134,7 +11316,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="C110">
         <v>581</v>
@@ -11217,7 +11399,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C111">
         <v>1000</v>
@@ -11300,7 +11482,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="C112">
         <v>661</v>
@@ -11383,7 +11565,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="C113">
         <v>331</v>
@@ -11466,7 +11648,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="C114">
         <v>1044</v>
@@ -11549,7 +11731,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="C115">
         <v>777</v>
@@ -11632,7 +11814,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="C116">
         <v>743</v>
@@ -11715,7 +11897,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="C117">
         <v>376</v>
@@ -11798,7 +11980,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C118">
         <v>745</v>
@@ -11881,7 +12063,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="C119">
         <v>697</v>
@@ -11964,7 +12146,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="C120">
         <v>831</v>
@@ -12047,7 +12229,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="C121">
         <v>698</v>
@@ -12130,7 +12312,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="C122">
         <v>590</v>
@@ -12213,7 +12395,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="C123">
         <v>452</v>
@@ -12296,7 +12478,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="C124">
         <v>407</v>
@@ -12379,7 +12561,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="C125">
         <v>961</v>
@@ -12462,7 +12644,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="C126">
         <v>657</v>
@@ -12545,7 +12727,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="C127">
         <v>295</v>
@@ -12628,7 +12810,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="C128">
         <v>1121</v>
@@ -12711,7 +12893,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="C129">
         <v>528</v>
@@ -12794,7 +12976,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="C130">
         <v>1067</v>
@@ -12877,7 +13059,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="C131">
         <v>1122</v>
@@ -12960,7 +13142,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="C132">
         <v>1081</v>
@@ -13043,7 +13225,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="C133">
         <v>1003</v>
@@ -13126,7 +13308,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="C134">
         <v>1006</v>
@@ -13209,7 +13391,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="C135">
         <v>600</v>
@@ -13292,7 +13474,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C136">
         <v>784</v>
@@ -13375,7 +13557,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="C137">
         <v>805</v>
@@ -13458,7 +13640,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="C138">
         <v>971</v>
@@ -13541,7 +13723,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="C139">
         <v>707</v>
@@ -13624,7 +13806,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="C140">
         <v>403</v>
@@ -13707,7 +13889,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C141">
         <v>553</v>
@@ -13790,7 +13972,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="C142">
         <v>292</v>
@@ -13873,7 +14055,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="C143">
         <v>859</v>
@@ -13956,7 +14138,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="C144">
         <v>830</v>
@@ -14039,7 +14221,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="C145">
         <v>485</v>
@@ -14122,7 +14304,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="C146">
         <v>1103</v>
@@ -14205,7 +14387,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="C147">
         <v>814</v>
@@ -14288,7 +14470,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="C148">
         <v>1042</v>
@@ -14371,7 +14553,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="C149">
         <v>977</v>
@@ -14454,7 +14636,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="C150">
         <v>672</v>
@@ -14537,7 +14719,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="C151">
         <v>738</v>
@@ -14620,7 +14802,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="C152">
         <v>829</v>
@@ -14703,7 +14885,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="C153">
         <v>926</v>
@@ -14786,7 +14968,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="C154">
         <v>553</v>
@@ -14869,7 +15051,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="C155">
         <v>1057</v>
@@ -14952,7 +15134,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="C156">
         <v>284</v>
@@ -15035,7 +15217,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="C157">
         <v>682</v>
@@ -15118,7 +15300,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="C158">
         <v>405</v>
@@ -15201,7 +15383,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C159">
         <v>1056</v>
@@ -15284,7 +15466,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C160">
         <v>838</v>
@@ -15367,7 +15549,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="C161">
         <v>751</v>
@@ -15450,7 +15632,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="C162">
         <v>436</v>
@@ -15533,7 +15715,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C163">
         <v>745</v>
@@ -15616,7 +15798,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="C164">
         <v>1101</v>
@@ -15699,7 +15881,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="C165">
         <v>848</v>
@@ -15782,7 +15964,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="C166">
         <v>620</v>
@@ -15865,7 +16047,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="C167">
         <v>615</v>
@@ -15948,7 +16130,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="C168">
         <v>1001</v>
@@ -16031,7 +16213,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="C169">
         <v>1059</v>
@@ -16114,7 +16296,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="C170">
         <v>750</v>
@@ -16197,7 +16379,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="C171">
         <v>739</v>
@@ -16280,7 +16462,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="C172">
         <v>625</v>
@@ -16363,7 +16545,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="C173">
         <v>724</v>
@@ -16446,7 +16628,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="C174">
         <v>974</v>
@@ -16529,7 +16711,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="C175">
         <v>789</v>
@@ -16612,7 +16794,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="C176">
         <v>921</v>
@@ -16695,7 +16877,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="C177">
         <v>1054</v>
@@ -16778,7 +16960,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C178">
         <v>1012</v>
@@ -16861,7 +17043,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="C179">
         <v>740</v>
@@ -16944,7 +17126,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="C180">
         <v>483</v>
@@ -17027,7 +17209,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="C181">
         <v>838</v>
@@ -17110,7 +17292,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="C182">
         <v>802</v>
@@ -17193,7 +17375,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="C183">
         <v>1024</v>
@@ -17276,7 +17458,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="C184">
         <v>615</v>
@@ -17359,7 +17541,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="C185">
         <v>607</v>
@@ -17442,7 +17624,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="C186">
         <v>327</v>
@@ -17525,7 +17707,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="C187">
         <v>654</v>
@@ -17608,7 +17790,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="C188">
         <v>813</v>
@@ -17691,7 +17873,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="C189">
         <v>872</v>
@@ -17774,7 +17956,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="C190">
         <v>762</v>
@@ -17857,7 +18039,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="C191">
         <v>804</v>
@@ -17940,7 +18122,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="C192">
         <v>697</v>
@@ -18023,7 +18205,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="C193">
         <v>720</v>
@@ -18106,7 +18288,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="C194">
         <v>803</v>
@@ -18189,7 +18371,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="C195">
         <v>840</v>
@@ -18272,7 +18454,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C196">
         <v>824</v>
@@ -18355,7 +18537,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="C197">
         <v>1017</v>
@@ -18438,7 +18620,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="C198">
         <v>1008</v>
@@ -18521,7 +18703,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="C199">
         <v>995</v>
@@ -18604,7 +18786,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="C200">
         <v>672</v>
@@ -18687,7 +18869,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="C201">
         <v>1115</v>
@@ -18770,7 +18952,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="C202">
         <v>886</v>
@@ -18853,7 +19035,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="C203">
         <v>704</v>
@@ -18936,7 +19118,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="C204">
         <v>1050</v>
@@ -19019,7 +19201,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="C205">
         <v>1086</v>
@@ -19102,7 +19284,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="C206">
         <v>291</v>
@@ -19185,7 +19367,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="C207">
         <v>649</v>
@@ -19268,7 +19450,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="C208">
         <v>630</v>
@@ -19351,7 +19533,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="C209">
         <v>1051</v>
@@ -19434,7 +19616,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="C210">
         <v>676</v>
@@ -19517,7 +19699,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="C211">
         <v>933</v>
@@ -19600,7 +19782,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="C212">
         <v>974</v>
@@ -19683,7 +19865,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="C213">
         <v>908</v>
@@ -19766,7 +19948,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="C214">
         <v>298</v>
@@ -19849,7 +20031,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="C215">
         <v>1086</v>
@@ -19932,7 +20114,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="C216">
         <v>404</v>
@@ -20015,7 +20197,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="C217">
         <v>727</v>
@@ -20098,7 +20280,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="C218">
         <v>993</v>
@@ -20181,7 +20363,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="C219">
         <v>498</v>
@@ -20264,7 +20446,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="C220">
         <v>586</v>
@@ -20347,7 +20529,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="C221">
         <v>766</v>
@@ -20430,7 +20612,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="C222">
         <v>434</v>
@@ -20513,7 +20695,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="C223">
         <v>471</v>
@@ -20596,7 +20778,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="C224">
         <v>672</v>
@@ -20679,7 +20861,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C225">
         <v>368</v>
@@ -20762,7 +20944,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="C226">
         <v>799</v>
@@ -20845,7 +21027,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="C227">
         <v>262</v>
@@ -20928,7 +21110,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="C228">
         <v>899</v>
@@ -21011,7 +21193,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="C229">
         <v>819</v>
@@ -21094,7 +21276,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="C230">
         <v>541</v>
@@ -21177,7 +21359,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="C231">
         <v>628</v>
@@ -21260,7 +21442,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="C232">
         <v>743</v>
@@ -21343,7 +21525,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="C233">
         <v>903</v>
@@ -21426,7 +21608,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="C234">
         <v>884</v>
@@ -21509,7 +21691,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="C235">
         <v>683</v>
@@ -21592,7 +21774,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="C236">
         <v>261</v>
@@ -21675,7 +21857,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="C237">
         <v>654</v>
@@ -21758,7 +21940,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="C238">
         <v>608</v>
@@ -21841,7 +22023,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="C239">
         <v>828</v>
@@ -21924,7 +22106,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="C240">
         <v>724</v>
@@ -22007,7 +22189,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="C241">
         <v>700</v>
@@ -22090,7 +22272,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="C242">
         <v>1003</v>
@@ -22173,7 +22355,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="C243">
         <v>389</v>
@@ -22256,7 +22438,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="C244">
         <v>435</v>
@@ -22339,7 +22521,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="C245">
         <v>820</v>
@@ -22422,7 +22604,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="C246">
         <v>916</v>
@@ -22505,7 +22687,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="C247">
         <v>725</v>
@@ -22588,7 +22770,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="C248">
         <v>1004</v>
@@ -22671,7 +22853,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="C249">
         <v>511</v>
@@ -22754,7 +22936,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="C250">
         <v>333</v>
@@ -22837,7 +23019,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="C251">
         <v>622</v>
@@ -22920,7 +23102,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="C252">
         <v>669</v>
@@ -23003,7 +23185,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="C253">
         <v>520</v>
@@ -23086,7 +23268,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="C254">
         <v>738</v>
@@ -23169,7 +23351,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="C255">
         <v>405</v>
@@ -23252,7 +23434,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="C256">
         <v>756</v>
@@ -23335,7 +23517,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C257">
         <v>714</v>
@@ -23418,7 +23600,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="C258">
         <v>1101</v>
@@ -23501,7 +23683,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="C259">
         <v>721</v>
@@ -23584,7 +23766,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="C260">
         <v>541</v>
@@ -23667,7 +23849,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="C261">
         <v>517</v>
@@ -23750,7 +23932,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="C262">
         <v>994</v>
@@ -23833,7 +24015,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="C263">
         <v>917</v>
@@ -23916,7 +24098,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="C264">
         <v>1054</v>
@@ -23999,7 +24181,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="C265">
         <v>830</v>
@@ -24082,7 +24264,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="C266">
         <v>911</v>
@@ -24165,7 +24347,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="C267">
         <v>802</v>
@@ -24248,7 +24430,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="C268">
         <v>610</v>
@@ -24331,7 +24513,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="C269">
         <v>873</v>
@@ -24414,7 +24596,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="C270">
         <v>374</v>
@@ -24497,7 +24679,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="C271">
         <v>791</v>
@@ -24580,7 +24762,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="C272">
         <v>581</v>
@@ -24663,7 +24845,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="C273">
         <v>970</v>
@@ -24746,7 +24928,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="C274">
         <v>1111</v>
@@ -24829,7 +25011,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="C275">
         <v>878</v>
@@ -24912,7 +25094,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="C276">
         <v>984</v>
@@ -24995,7 +25177,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="C277">
         <v>648</v>
@@ -25078,7 +25260,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="C278">
         <v>869</v>
@@ -25161,7 +25343,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="C279">
         <v>300</v>
@@ -25244,7 +25426,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="C280">
         <v>508</v>
@@ -25327,7 +25509,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="C281">
         <v>972</v>
@@ -25410,7 +25592,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="C282">
         <v>1137</v>
@@ -25493,7 +25675,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="C283">
         <v>402</v>
@@ -25576,7 +25758,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="C284">
         <v>1032</v>
@@ -25659,7 +25841,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="C285">
         <v>773</v>
@@ -25742,7 +25924,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="C286">
         <v>970</v>
@@ -25825,7 +26007,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="C287">
         <v>982</v>
@@ -25908,7 +26090,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="C288">
         <v>981</v>
@@ -25991,7 +26173,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="C289">
         <v>594</v>
@@ -26074,7 +26256,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="C290">
         <v>983</v>
@@ -26157,7 +26339,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="C291">
         <v>303</v>
@@ -26240,7 +26422,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="C292">
         <v>844</v>
@@ -26323,7 +26505,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="C293">
         <v>666</v>
@@ -26406,7 +26588,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="C294">
         <v>999</v>
@@ -26489,7 +26671,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="C295">
         <v>1059</v>
@@ -26572,7 +26754,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="C296">
         <v>860</v>
@@ -26655,7 +26837,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="C297">
         <v>752</v>
@@ -26738,7 +26920,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="C298">
         <v>1085</v>
@@ -26821,7 +27003,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="C299">
         <v>993</v>
@@ -26904,7 +27086,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="C300">
         <v>1061</v>
@@ -26987,7 +27169,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="C301">
         <v>1137</v>
@@ -27070,7 +27252,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="C302">
         <v>635</v>
@@ -27153,7 +27335,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="C303">
         <v>1041</v>
@@ -27236,7 +27418,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="C304">
         <v>604</v>
@@ -27319,7 +27501,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="C305">
         <v>557</v>
@@ -27402,7 +27584,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="C306">
         <v>852</v>
@@ -27485,7 +27667,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="C307">
         <v>624</v>
@@ -27568,7 +27750,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="C308">
         <v>450</v>
@@ -27651,7 +27833,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="C309">
         <v>672</v>
@@ -27734,7 +27916,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="C310">
         <v>1023</v>
@@ -27817,7 +27999,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="C311">
         <v>1013</v>
@@ -27900,7 +28082,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="C312">
         <v>775</v>
@@ -27983,7 +28165,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="C313">
         <v>780</v>
@@ -28066,7 +28248,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="C314">
         <v>557</v>
@@ -28149,7 +28331,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="C315">
         <v>875</v>
@@ -28232,7 +28414,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="C316">
         <v>741</v>
@@ -28315,7 +28497,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="C317">
         <v>650</v>
@@ -28398,7 +28580,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="C318">
         <v>625</v>
@@ -28481,7 +28663,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="C319">
         <v>1020</v>
@@ -28564,7 +28746,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="C320">
         <v>536</v>
@@ -28647,7 +28829,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="C321">
         <v>438</v>
@@ -28730,7 +28912,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="C322">
         <v>587</v>
@@ -28813,7 +28995,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="C323">
         <v>924</v>
@@ -28896,7 +29078,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="C324">
         <v>751</v>
@@ -28979,7 +29161,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="C325">
         <v>616</v>
@@ -29062,7 +29244,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="C326">
         <v>637</v>
@@ -29145,7 +29327,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="C327">
         <v>883</v>
@@ -29228,7 +29410,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="C328">
         <v>407</v>
@@ -29311,7 +29493,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="C329">
         <v>846</v>
@@ -29394,7 +29576,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="C330">
         <v>825</v>
@@ -29477,7 +29659,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="C331">
         <v>818</v>
@@ -29560,7 +29742,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="C332">
         <v>495</v>
@@ -29643,7 +29825,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="C333">
         <v>794</v>
@@ -29726,7 +29908,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="C334">
         <v>1074</v>
@@ -29809,7 +29991,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="C335">
         <v>988</v>
@@ -29892,7 +30074,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C336">
         <v>1011</v>
@@ -29975,7 +30157,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="C337">
         <v>893</v>
@@ -30058,7 +30240,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="C338">
         <v>718</v>
@@ -30141,7 +30323,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="C339">
         <v>916</v>
@@ -30224,7 +30406,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="C340">
         <v>511</v>
@@ -30307,7 +30489,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="C341">
         <v>919</v>
@@ -30390,7 +30572,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="C342">
         <v>512</v>
@@ -30473,7 +30655,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="C343">
         <v>679</v>
@@ -30556,7 +30738,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="C344">
         <v>717</v>
@@ -30639,7 +30821,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="C345">
         <v>372</v>
@@ -30722,7 +30904,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="C346">
         <v>1110</v>
@@ -30805,7 +30987,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="C347">
         <v>920</v>
@@ -30888,7 +31070,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="C348">
         <v>681</v>
@@ -30971,7 +31153,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="C349">
         <v>641</v>
@@ -31054,7 +31236,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="C350">
         <v>236</v>
@@ -31137,7 +31319,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="C351">
         <v>803</v>
@@ -31220,7 +31402,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="C352">
         <v>464</v>
@@ -31303,7 +31485,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="C353">
         <v>899</v>
@@ -31386,7 +31568,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="C354">
         <v>620</v>
@@ -31469,7 +31651,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="C355">
         <v>594</v>
@@ -31552,7 +31734,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="C356">
         <v>716</v>
@@ -31635,7 +31817,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="C357">
         <v>586</v>
@@ -31718,7 +31900,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="C358">
         <v>1105</v>
@@ -31801,7 +31983,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="C359">
         <v>1240</v>
@@ -31884,7 +32066,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="C360">
         <v>1074</v>
@@ -31967,7 +32149,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="C361">
         <v>875</v>
@@ -32050,7 +32232,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="C362">
         <v>1071</v>
@@ -32133,7 +32315,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="C363">
         <v>831</v>
@@ -32216,7 +32398,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="C364">
         <v>844</v>
@@ -32299,7 +32481,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="C365">
         <v>850</v>
@@ -32382,7 +32564,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="C366">
         <v>1104</v>
@@ -32465,7 +32647,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="C367">
         <v>654</v>
@@ -32548,7 +32730,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="C368">
         <v>616</v>
@@ -32631,7 +32813,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="C369">
         <v>1016</v>
@@ -32714,7 +32896,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="C370">
         <v>1133</v>
@@ -32797,7 +32979,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="C371">
         <v>1118</v>
@@ -32880,7 +33062,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="C372">
         <v>1082</v>
@@ -32963,7 +33145,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="C373">
         <v>1051</v>
@@ -33046,7 +33228,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="C374">
         <v>1046</v>
@@ -33129,7 +33311,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="C375">
         <v>851</v>
@@ -33212,7 +33394,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="C376">
         <v>1042</v>
@@ -33295,7 +33477,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="C377">
         <v>867</v>
@@ -33378,7 +33560,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="C378">
         <v>547</v>
@@ -33461,7 +33643,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="C379">
         <v>652</v>
@@ -33544,7 +33726,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="C380">
         <v>621</v>
@@ -33627,7 +33809,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="C381">
         <v>561</v>
@@ -33710,7 +33892,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="C382">
         <v>615</v>
@@ -33793,7 +33975,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="C383">
         <v>556</v>
@@ -33876,7 +34058,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="C384">
         <v>800</v>
@@ -33959,7 +34141,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="C385">
         <v>592</v>
@@ -34042,7 +34224,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="C386">
         <v>1166</v>
@@ -34125,7 +34307,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="C387">
         <v>1108</v>
@@ -34208,7 +34390,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="C388">
         <v>1054</v>
@@ -34291,7 +34473,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="C389">
         <v>366</v>
@@ -34374,7 +34556,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="C390">
         <v>408</v>
@@ -34457,7 +34639,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="C391">
         <v>565</v>
@@ -34540,7 +34722,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="C392">
         <v>818</v>
@@ -34623,7 +34805,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="C393">
         <v>856</v>
@@ -34706,7 +34888,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="C394">
         <v>898</v>
@@ -34789,7 +34971,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C395">
         <v>874</v>
@@ -34872,7 +35054,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="C396">
         <v>684</v>
@@ -34955,7 +35137,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="C397">
         <v>589</v>
@@ -35038,7 +35220,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C398">
         <v>1063</v>
@@ -35121,7 +35303,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="C399">
         <v>804</v>
@@ -35204,7 +35386,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="C400">
         <v>410</v>
@@ -35287,7 +35469,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="C401">
         <v>905</v>
@@ -35370,7 +35552,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="C402">
         <v>843</v>
@@ -35453,7 +35635,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="C403">
         <v>1144</v>
@@ -35536,7 +35718,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="C404">
         <v>707</v>
@@ -35619,7 +35801,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="C405">
         <v>544</v>
@@ -35702,7 +35884,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="C406">
         <v>947</v>
@@ -35785,7 +35967,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="C407">
         <v>735</v>
@@ -35868,7 +36050,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="C408">
         <v>1053</v>
@@ -35951,7 +36133,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="C409">
         <v>378</v>
@@ -36034,7 +36216,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="C410">
         <v>1086</v>
@@ -36117,7 +36299,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="C411">
         <v>682</v>
@@ -36200,7 +36382,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="C412">
         <v>757</v>
@@ -36283,7 +36465,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="C413">
         <v>694</v>
@@ -36366,7 +36548,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="C414">
         <v>605</v>
@@ -36449,7 +36631,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="C415">
         <v>559</v>
@@ -36532,7 +36714,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="C416">
         <v>840</v>
@@ -36615,7 +36797,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="C417">
         <v>634</v>
@@ -36698,7 +36880,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="C418">
         <v>580</v>
@@ -36781,7 +36963,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="C419">
         <v>316</v>
@@ -36864,7 +37046,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="C420">
         <v>864</v>
@@ -36947,7 +37129,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="C421">
         <v>462</v>
@@ -37030,7 +37212,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="C422">
         <v>394</v>
@@ -37113,7 +37295,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="C423">
         <v>605</v>
@@ -37196,7 +37378,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="C424">
         <v>551</v>
@@ -37279,7 +37461,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="C425">
         <v>548</v>
@@ -37362,7 +37544,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="C426">
         <v>848</v>
@@ -37445,7 +37627,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="C427">
         <v>768</v>
@@ -37528,7 +37710,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="C428">
         <v>573</v>
@@ -37611,7 +37793,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="C429">
         <v>461</v>
@@ -37694,7 +37876,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="C430">
         <v>1106</v>
@@ -37777,7 +37959,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="C431">
         <v>473</v>
@@ -37860,7 +38042,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>430</v>
+        <v>456</v>
       </c>
       <c r="C432">
         <v>1077</v>
@@ -37943,7 +38125,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="C433">
         <v>697</v>
@@ -38026,7 +38208,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="C434">
         <v>439</v>
@@ -38109,7 +38291,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="C435">
         <v>829</v>
@@ -38192,7 +38374,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="C436">
         <v>772</v>
@@ -38275,7 +38457,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="C437">
         <v>1024</v>
@@ -38358,7 +38540,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="C438">
         <v>1119</v>
@@ -38441,7 +38623,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>437</v>
+        <v>463</v>
       </c>
       <c r="C439">
         <v>1057</v>
@@ -38524,7 +38706,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="C440">
         <v>893</v>
@@ -38607,7 +38789,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="C441">
         <v>815</v>
@@ -38690,7 +38872,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="C442">
         <v>778</v>
@@ -38773,7 +38955,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="C443">
         <v>799</v>
@@ -38856,7 +39038,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="C444">
         <v>551</v>
@@ -38939,7 +39121,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="C445">
         <v>983</v>
@@ -39022,7 +39204,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="C446">
         <v>1026</v>
@@ -39105,7 +39287,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="C447">
         <v>422</v>
@@ -39188,7 +39370,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="C448">
         <v>420</v>
@@ -39271,7 +39453,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>447</v>
+        <v>473</v>
       </c>
       <c r="C449">
         <v>769</v>
@@ -39354,7 +39536,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="C450">
         <v>636</v>
@@ -39437,7 +39619,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="C451">
         <v>997</v>
@@ -39520,7 +39702,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="C452">
         <v>865</v>
@@ -39603,7 +39785,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="C453">
         <v>1117</v>
@@ -39686,7 +39868,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="C454">
         <v>918</v>
@@ -39769,7 +39951,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="C455">
         <v>518</v>
@@ -39852,7 +40034,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="C456">
         <v>753</v>
@@ -39935,7 +40117,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="C457">
         <v>577</v>
@@ -40018,7 +40200,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="C458">
         <v>783</v>
@@ -40101,7 +40283,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="C459">
         <v>303</v>
@@ -40184,7 +40366,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="C460">
         <v>672</v>
@@ -40267,7 +40449,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="C461">
         <v>505</v>
@@ -40350,7 +40532,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="C462">
         <v>815</v>
@@ -40433,7 +40615,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>461</v>
+        <v>487</v>
       </c>
       <c r="C463">
         <v>768</v>
@@ -40516,7 +40698,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>462</v>
+        <v>488</v>
       </c>
       <c r="C464">
         <v>772</v>
@@ -40599,7 +40781,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
       <c r="C465">
         <v>435</v>
@@ -40682,7 +40864,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="C466">
         <v>669</v>
@@ -40765,7 +40947,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="s">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="C467">
         <v>549</v>
@@ -40848,7 +41030,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
       <c r="C468">
         <v>1025</v>
@@ -40931,7 +41113,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="s">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="C469">
         <v>1074</v>
@@ -41014,7 +41196,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="s">
-        <v>468</v>
+        <v>494</v>
       </c>
       <c r="C470">
         <v>967</v>
@@ -41097,7 +41279,7 @@
         <v>469</v>
       </c>
       <c r="B471" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
       <c r="C471">
         <v>896</v>
@@ -41180,7 +41362,7 @@
         <v>470</v>
       </c>
       <c r="B472" t="s">
-        <v>470</v>
+        <v>496</v>
       </c>
       <c r="C472">
         <v>669</v>
@@ -41263,7 +41445,7 @@
         <v>471</v>
       </c>
       <c r="B473" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="C473">
         <v>383</v>
@@ -41346,7 +41528,7 @@
         <v>472</v>
       </c>
       <c r="B474" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
       <c r="C474">
         <v>760</v>
@@ -41429,7 +41611,7 @@
         <v>473</v>
       </c>
       <c r="B475" t="s">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="C475">
         <v>1001</v>
@@ -41512,7 +41694,7 @@
         <v>474</v>
       </c>
       <c r="B476" t="s">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="C476">
         <v>1034</v>
@@ -41595,7 +41777,7 @@
         <v>475</v>
       </c>
       <c r="B477" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C477">
         <v>634</v>
@@ -41678,7 +41860,7 @@
         <v>476</v>
       </c>
       <c r="B478" t="s">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="C478">
         <v>727</v>
@@ -41761,7 +41943,7 @@
         <v>477</v>
       </c>
       <c r="B479" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="C479">
         <v>766</v>
@@ -41844,7 +42026,7 @@
         <v>478</v>
       </c>
       <c r="B480" t="s">
-        <v>478</v>
+        <v>504</v>
       </c>
       <c r="C480">
         <v>596</v>
@@ -41927,7 +42109,7 @@
         <v>479</v>
       </c>
       <c r="B481" t="s">
-        <v>479</v>
+        <v>505</v>
       </c>
       <c r="C481">
         <v>416</v>
@@ -42010,7 +42192,7 @@
         <v>480</v>
       </c>
       <c r="B482" t="s">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="C482">
         <v>1056</v>
@@ -42093,7 +42275,7 @@
         <v>481</v>
       </c>
       <c r="B483" t="s">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="C483">
         <v>1061</v>
@@ -42176,7 +42358,7 @@
         <v>482</v>
       </c>
       <c r="B484" t="s">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="C484">
         <v>653</v>
@@ -42259,7 +42441,7 @@
         <v>483</v>
       </c>
       <c r="B485" t="s">
-        <v>483</v>
+        <v>509</v>
       </c>
       <c r="C485">
         <v>551</v>
@@ -42342,7 +42524,7 @@
         <v>484</v>
       </c>
       <c r="B486" t="s">
-        <v>484</v>
+        <v>510</v>
       </c>
       <c r="C486">
         <v>882</v>
@@ -42425,7 +42607,7 @@
         <v>485</v>
       </c>
       <c r="B487" t="s">
-        <v>485</v>
+        <v>511</v>
       </c>
       <c r="C487">
         <v>604</v>
@@ -42508,7 +42690,7 @@
         <v>486</v>
       </c>
       <c r="B488" t="s">
-        <v>486</v>
+        <v>512</v>
       </c>
       <c r="C488">
         <v>329</v>
@@ -42591,7 +42773,7 @@
         <v>487</v>
       </c>
       <c r="B489" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="C489">
         <v>762</v>
@@ -42674,7 +42856,7 @@
         <v>488</v>
       </c>
       <c r="B490" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="C490">
         <v>726</v>
@@ -42757,7 +42939,7 @@
         <v>489</v>
       </c>
       <c r="B491" t="s">
-        <v>489</v>
+        <v>515</v>
       </c>
       <c r="C491">
         <v>952</v>
@@ -42840,7 +43022,7 @@
         <v>490</v>
       </c>
       <c r="B492" t="s">
-        <v>490</v>
+        <v>516</v>
       </c>
       <c r="C492">
         <v>590</v>
@@ -42923,7 +43105,7 @@
         <v>491</v>
       </c>
       <c r="B493" t="s">
-        <v>491</v>
+        <v>517</v>
       </c>
       <c r="C493">
         <v>374</v>
@@ -43006,7 +43188,7 @@
         <v>492</v>
       </c>
       <c r="B494" t="s">
-        <v>492</v>
+        <v>518</v>
       </c>
       <c r="C494">
         <v>911</v>
@@ -43089,7 +43271,7 @@
         <v>493</v>
       </c>
       <c r="B495" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="C495">
         <v>711</v>
@@ -43172,7 +43354,7 @@
         <v>494</v>
       </c>
       <c r="B496" t="s">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="C496">
         <v>832</v>
@@ -43255,7 +43437,7 @@
         <v>495</v>
       </c>
       <c r="B497" t="s">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="C497">
         <v>916</v>
@@ -43338,7 +43520,7 @@
         <v>496</v>
       </c>
       <c r="B498" t="s">
-        <v>496</v>
+        <v>522</v>
       </c>
       <c r="C498">
         <v>836</v>
@@ -43421,7 +43603,7 @@
         <v>497</v>
       </c>
       <c r="B499" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="C499">
         <v>845</v>
@@ -43504,7 +43686,7 @@
         <v>498</v>
       </c>
       <c r="B500" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="C500">
         <v>866</v>
@@ -43587,7 +43769,7 @@
         <v>499</v>
       </c>
       <c r="B501" t="s">
-        <v>499</v>
+        <v>525</v>
       </c>
       <c r="C501">
         <v>793</v>
@@ -43670,7 +43852,7 @@
         <v>500</v>
       </c>
       <c r="B502" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C502">
         <v>816</v>
@@ -43753,7 +43935,7 @@
         <v>501</v>
       </c>
       <c r="B503" t="s">
-        <v>501</v>
+        <v>527</v>
       </c>
       <c r="C503">
         <v>806</v>
@@ -43836,7 +44018,7 @@
         <v>502</v>
       </c>
       <c r="B504" t="s">
-        <v>502</v>
+        <v>528</v>
       </c>
       <c r="C504">
         <v>827</v>
@@ -43919,7 +44101,7 @@
         <v>503</v>
       </c>
       <c r="B505" t="s">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="C505">
         <v>693</v>
@@ -44002,7 +44184,7 @@
         <v>504</v>
       </c>
       <c r="B506" t="s">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="C506">
         <v>748</v>
@@ -44085,7 +44267,7 @@
         <v>505</v>
       </c>
       <c r="B507" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="C507">
         <v>1019</v>
@@ -44168,7 +44350,7 @@
         <v>506</v>
       </c>
       <c r="B508" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="C508">
         <v>891</v>
@@ -44251,7 +44433,7 @@
         <v>507</v>
       </c>
       <c r="B509" t="s">
-        <v>507</v>
+        <v>533</v>
       </c>
       <c r="C509">
         <v>846</v>
@@ -44334,7 +44516,7 @@
         <v>508</v>
       </c>
       <c r="B510" t="s">
-        <v>508</v>
+        <v>534</v>
       </c>
       <c r="C510">
         <v>1078</v>
@@ -44417,7 +44599,7 @@
         <v>509</v>
       </c>
       <c r="B511" t="s">
-        <v>509</v>
+        <v>535</v>
       </c>
       <c r="C511">
         <v>1020</v>
@@ -44500,7 +44682,7 @@
         <v>510</v>
       </c>
       <c r="B512" t="s">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="C512">
         <v>1030</v>
@@ -44583,7 +44765,7 @@
         <v>511</v>
       </c>
       <c r="B513" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="C513">
         <v>1146</v>
@@ -44666,7 +44848,7 @@
         <v>512</v>
       </c>
       <c r="B514" t="s">
-        <v>512</v>
+        <v>538</v>
       </c>
       <c r="C514">
         <v>619</v>
@@ -44749,7 +44931,7 @@
         <v>513</v>
       </c>
       <c r="B515" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="C515">
         <v>586</v>
@@ -44832,7 +45014,7 @@
         <v>514</v>
       </c>
       <c r="B516" t="s">
-        <v>514</v>
+        <v>540</v>
       </c>
       <c r="C516">
         <v>833</v>
@@ -44915,7 +45097,7 @@
         <v>515</v>
       </c>
       <c r="B517" t="s">
-        <v>515</v>
+        <v>541</v>
       </c>
       <c r="C517">
         <v>846</v>
@@ -44998,7 +45180,7 @@
         <v>516</v>
       </c>
       <c r="B518" t="s">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="C518">
         <v>888</v>
@@ -45081,7 +45263,7 @@
         <v>517</v>
       </c>
       <c r="B519" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="C519">
         <v>643</v>
@@ -45164,7 +45346,7 @@
         <v>518</v>
       </c>
       <c r="B520" t="s">
-        <v>518</v>
+        <v>544</v>
       </c>
       <c r="C520">
         <v>631</v>
@@ -45247,7 +45429,7 @@
         <v>519</v>
       </c>
       <c r="B521" t="s">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="C521">
         <v>1017</v>
@@ -45330,7 +45512,7 @@
         <v>520</v>
       </c>
       <c r="B522" t="s">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="C522">
         <v>953</v>
@@ -45413,7 +45595,7 @@
         <v>521</v>
       </c>
       <c r="B523" t="s">
-        <v>521</v>
+        <v>547</v>
       </c>
       <c r="C523">
         <v>1118</v>
@@ -45496,7 +45678,7 @@
         <v>522</v>
       </c>
       <c r="B524" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="C524">
         <v>980</v>
@@ -45579,7 +45761,7 @@
         <v>523</v>
       </c>
       <c r="B525" t="s">
-        <v>523</v>
+        <v>549</v>
       </c>
       <c r="C525">
         <v>839</v>
@@ -45662,7 +45844,7 @@
         <v>524</v>
       </c>
       <c r="B526" t="s">
-        <v>524</v>
+        <v>550</v>
       </c>
       <c r="C526">
         <v>813</v>
@@ -45745,7 +45927,7 @@
         <v>525</v>
       </c>
       <c r="B527" t="s">
-        <v>525</v>
+        <v>551</v>
       </c>
       <c r="C527">
         <v>791</v>
@@ -45828,7 +46010,7 @@
         <v>526</v>
       </c>
       <c r="B528" t="s">
-        <v>526</v>
+        <v>552</v>
       </c>
       <c r="C528">
         <v>1084</v>
@@ -45911,7 +46093,7 @@
         <v>527</v>
       </c>
       <c r="B529" t="s">
-        <v>527</v>
+        <v>553</v>
       </c>
       <c r="C529">
         <v>1013</v>
@@ -45994,7 +46176,7 @@
         <v>528</v>
       </c>
       <c r="B530" t="s">
-        <v>528</v>
+        <v>554</v>
       </c>
       <c r="C530">
         <v>788</v>
@@ -46077,7 +46259,7 @@
         <v>529</v>
       </c>
       <c r="B531" t="s">
-        <v>529</v>
+        <v>555</v>
       </c>
       <c r="C531">
         <v>823</v>
@@ -46160,7 +46342,7 @@
         <v>530</v>
       </c>
       <c r="B532" t="s">
-        <v>530</v>
+        <v>556</v>
       </c>
       <c r="C532">
         <v>1017</v>
@@ -46243,7 +46425,7 @@
         <v>531</v>
       </c>
       <c r="B533" t="s">
-        <v>531</v>
+        <v>557</v>
       </c>
       <c r="C533">
         <v>841</v>
@@ -46326,7 +46508,7 @@
         <v>532</v>
       </c>
       <c r="B534" t="s">
-        <v>532</v>
+        <v>558</v>
       </c>
       <c r="C534">
         <v>834</v>
@@ -46409,7 +46591,7 @@
         <v>533</v>
       </c>
       <c r="B535" t="s">
-        <v>533</v>
+        <v>559</v>
       </c>
       <c r="C535">
         <v>821</v>
@@ -46492,7 +46674,7 @@
         <v>534</v>
       </c>
       <c r="B536" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="C536">
         <v>834</v>
@@ -46575,7 +46757,7 @@
         <v>535</v>
       </c>
       <c r="B537" t="s">
-        <v>535</v>
+        <v>561</v>
       </c>
       <c r="C537">
         <v>841</v>
@@ -46658,7 +46840,7 @@
         <v>536</v>
       </c>
       <c r="B538" t="s">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="C538">
         <v>771</v>
@@ -46741,7 +46923,7 @@
         <v>537</v>
       </c>
       <c r="B539" t="s">
-        <v>537</v>
+        <v>563</v>
       </c>
       <c r="C539">
         <v>896</v>
@@ -46824,7 +47006,7 @@
         <v>538</v>
       </c>
       <c r="B540" t="s">
-        <v>538</v>
+        <v>564</v>
       </c>
       <c r="C540">
         <v>818</v>
@@ -46907,7 +47089,7 @@
         <v>539</v>
       </c>
       <c r="B541" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="C541">
         <v>1111</v>
@@ -46990,7 +47172,7 @@
         <v>540</v>
       </c>
       <c r="B542" t="s">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="C542">
         <v>860</v>
@@ -47073,7 +47255,7 @@
         <v>541</v>
       </c>
       <c r="B543" t="s">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="C543">
         <v>806</v>
@@ -47156,7 +47338,7 @@
         <v>542</v>
       </c>
       <c r="B544" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="C544">
         <v>803</v>
@@ -47239,7 +47421,7 @@
         <v>543</v>
       </c>
       <c r="B545" t="s">
-        <v>543</v>
+        <v>569</v>
       </c>
       <c r="C545">
         <v>576</v>
@@ -47322,7 +47504,7 @@
         <v>544</v>
       </c>
       <c r="B546" t="s">
-        <v>544</v>
+        <v>570</v>
       </c>
       <c r="C546">
         <v>943</v>
@@ -47405,7 +47587,7 @@
         <v>545</v>
       </c>
       <c r="B547" t="s">
-        <v>545</v>
+        <v>571</v>
       </c>
       <c r="C547">
         <v>725</v>
@@ -47488,7 +47670,7 @@
         <v>546</v>
       </c>
       <c r="B548" t="s">
-        <v>546</v>
+        <v>572</v>
       </c>
       <c r="C548">
         <v>1017</v>
@@ -47571,7 +47753,7 @@
         <v>547</v>
       </c>
       <c r="B549" t="s">
-        <v>547</v>
+        <v>573</v>
       </c>
       <c r="C549">
         <v>674</v>
@@ -47654,7 +47836,7 @@
         <v>548</v>
       </c>
       <c r="B550" t="s">
-        <v>548</v>
+        <v>574</v>
       </c>
       <c r="C550">
         <v>615</v>
@@ -47737,7 +47919,7 @@
         <v>549</v>
       </c>
       <c r="B551" t="s">
-        <v>549</v>
+        <v>575</v>
       </c>
       <c r="C551">
         <v>880</v>
@@ -47820,7 +48002,7 @@
         <v>550</v>
       </c>
       <c r="B552" t="s">
-        <v>550</v>
+        <v>576</v>
       </c>
       <c r="C552">
         <v>615</v>
@@ -47903,7 +48085,7 @@
         <v>551</v>
       </c>
       <c r="B553" t="s">
-        <v>551</v>
+        <v>577</v>
       </c>
       <c r="C553">
         <v>952</v>
@@ -47986,7 +48168,7 @@
         <v>552</v>
       </c>
       <c r="B554" t="s">
-        <v>552</v>
+        <v>578</v>
       </c>
       <c r="C554">
         <v>868</v>
@@ -48069,7 +48251,7 @@
         <v>553</v>
       </c>
       <c r="B555" t="s">
-        <v>553</v>
+        <v>579</v>
       </c>
       <c r="C555">
         <v>579</v>
@@ -48152,7 +48334,7 @@
         <v>554</v>
       </c>
       <c r="B556" t="s">
-        <v>554</v>
+        <v>580</v>
       </c>
       <c r="C556">
         <v>428</v>
@@ -48235,7 +48417,7 @@
         <v>555</v>
       </c>
       <c r="B557" t="s">
-        <v>555</v>
+        <v>581</v>
       </c>
       <c r="C557">
         <v>881</v>
@@ -48318,7 +48500,7 @@
         <v>556</v>
       </c>
       <c r="B558" t="s">
-        <v>556</v>
+        <v>582</v>
       </c>
       <c r="C558">
         <v>1017</v>
@@ -48401,7 +48583,7 @@
         <v>557</v>
       </c>
       <c r="B559" t="s">
-        <v>557</v>
+        <v>583</v>
       </c>
       <c r="C559">
         <v>775</v>
@@ -48484,7 +48666,7 @@
         <v>558</v>
       </c>
       <c r="B560" t="s">
-        <v>558</v>
+        <v>584</v>
       </c>
       <c r="C560">
         <v>791</v>
@@ -48567,7 +48749,7 @@
         <v>559</v>
       </c>
       <c r="B561" t="s">
-        <v>559</v>
+        <v>585</v>
       </c>
       <c r="C561">
         <v>725</v>
@@ -48650,7 +48832,7 @@
         <v>560</v>
       </c>
       <c r="B562" t="s">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="C562">
         <v>1039</v>
@@ -48733,7 +48915,7 @@
         <v>561</v>
       </c>
       <c r="B563" t="s">
-        <v>561</v>
+        <v>587</v>
       </c>
       <c r="C563">
         <v>956</v>
@@ -48816,7 +48998,7 @@
         <v>562</v>
       </c>
       <c r="B564" t="s">
-        <v>562</v>
+        <v>588</v>
       </c>
       <c r="C564">
         <v>603</v>
@@ -48899,7 +49081,7 @@
         <v>563</v>
       </c>
       <c r="B565" t="s">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="C565">
         <v>626</v>
@@ -48982,7 +49164,7 @@
         <v>564</v>
       </c>
       <c r="B566" t="s">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="C566">
         <v>505</v>
@@ -49065,7 +49247,7 @@
         <v>565</v>
       </c>
       <c r="B567" t="s">
-        <v>565</v>
+        <v>591</v>
       </c>
       <c r="C567">
         <v>746</v>
@@ -49148,7 +49330,7 @@
         <v>566</v>
       </c>
       <c r="B568" t="s">
-        <v>566</v>
+        <v>592</v>
       </c>
       <c r="C568">
         <v>962</v>
@@ -49231,7 +49413,7 @@
         <v>567</v>
       </c>
       <c r="B569" t="s">
-        <v>567</v>
+        <v>593</v>
       </c>
       <c r="C569">
         <v>883</v>
@@ -49314,7 +49496,7 @@
         <v>568</v>
       </c>
       <c r="B570" t="s">
-        <v>568</v>
+        <v>594</v>
       </c>
       <c r="C570">
         <v>886</v>
@@ -49397,7 +49579,7 @@
         <v>569</v>
       </c>
       <c r="B571" t="s">
-        <v>569</v>
+        <v>595</v>
       </c>
       <c r="C571">
         <v>611</v>
@@ -49480,7 +49662,7 @@
         <v>570</v>
       </c>
       <c r="B572" t="s">
-        <v>570</v>
+        <v>596</v>
       </c>
       <c r="C572">
         <v>580</v>
@@ -49563,7 +49745,7 @@
         <v>571</v>
       </c>
       <c r="B573" t="s">
-        <v>571</v>
+        <v>597</v>
       </c>
       <c r="C573">
         <v>896</v>
@@ -49646,7 +49828,7 @@
         <v>572</v>
       </c>
       <c r="B574" t="s">
-        <v>572</v>
+        <v>598</v>
       </c>
       <c r="C574">
         <v>1026</v>
@@ -49729,7 +49911,7 @@
         <v>573</v>
       </c>
       <c r="B575" t="s">
-        <v>573</v>
+        <v>599</v>
       </c>
       <c r="C575">
         <v>903</v>
@@ -49812,7 +49994,7 @@
         <v>574</v>
       </c>
       <c r="B576" t="s">
-        <v>574</v>
+        <v>600</v>
       </c>
       <c r="C576">
         <v>851</v>
@@ -49895,7 +50077,7 @@
         <v>575</v>
       </c>
       <c r="B577" t="s">
-        <v>575</v>
+        <v>601</v>
       </c>
       <c r="C577">
         <v>905</v>
@@ -49978,7 +50160,7 @@
         <v>576</v>
       </c>
       <c r="B578" t="s">
-        <v>576</v>
+        <v>602</v>
       </c>
       <c r="C578">
         <v>310</v>
@@ -50061,7 +50243,7 @@
         <v>577</v>
       </c>
       <c r="B579" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="C579">
         <v>524</v>
@@ -50144,7 +50326,7 @@
         <v>578</v>
       </c>
       <c r="B580" t="s">
-        <v>578</v>
+        <v>604</v>
       </c>
       <c r="C580">
         <v>910</v>
@@ -50227,7 +50409,7 @@
         <v>579</v>
       </c>
       <c r="B581" t="s">
-        <v>579</v>
+        <v>605</v>
       </c>
       <c r="C581">
         <v>913</v>
